--- a/공고누적.xlsx
+++ b/공고누적.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고누적" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고누적'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고누적'!$A$1:$G$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>부산테크노파크</t>
+          <t>중소벤처기업부</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Age-Tech 종합지원센터 운영 사업 TRL기반 기술성장 맞춤 지원 공고</t>
+          <t>2026년 중소기업 스마트서비스 지원사업 참여기업 모집 공고(A/S지원)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -514,12 +514,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Age-Tech</t>
+          <t>스마트</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>중소벤처기업부</t>
+          <t>저출산고령사회위원회</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026년 중소기업 스마트서비스 지원사업 참여기업 모집 공고(A/S지원)</t>
+          <t>저출산고령사회위원회 홈페이지 일시중단 안내</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -551,12 +551,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>스마트</t>
+          <t>고령</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>저출산고령사회위원회</t>
+          <t>부산테크노파크</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>저출산고령사회위원회 홈페이지 일시중단 안내</t>
+          <t>Age-Tech 종합지원센터 운영 사업 TRL기반 기술성장 맞춤 지원 공고</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>고령</t>
+          <t>Age-Tech</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>부산정보산업진흥원</t>
+          <t>중앙사회서비스원</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2026년 AX 에이지테크 시장확산 지원사업 모집 공고</t>
+          <t>2026년 사회서비스 종사자 심리상담 지원사업 3기 참여자 모집(~9/30) 2026-09-01 293</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>에이지테크, AX</t>
+          <t>사회서비스</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -795,12 +795,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>부산정보산업진흥원</t>
+          <t>중소벤처기업부</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026 해양문화도시 기반의 에이지테크 실증거점 조성 사업 「CES 2027 통합 부산관」 참가기업 모집 공고</t>
+          <t>『중소기업 AX 우수사례 공모전』참가기업 모집 공고</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>에이지테크, 실증</t>
+          <t>AX</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>부산테크노파크</t>
+          <t>중소벤처기업부</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026년 고위험산업 사각지대 집중관리사업(안전보호구 지원) 참여기업 4차 추가모집 공고</t>
+          <t>「지역 중소기업 AI 활용·확산 유공 포상」 후보자 모집 공고</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>유공, 포상</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>부산안전산업존(BSI-Zone) 초기창업자 2차 모집공고</t>
+          <t>2026년 고위험산업 사각지대 집중관리사업(안전보호구 지원) 참여기업 4차 추가모집 공고</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>광주테크노파크</t>
+          <t>부산테크노파크</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>「2026년도 연구개발특구진흥재단 광주특구본부」 지역혁신 실증 프로젝트 기획 실증의제 수요조사 공고(2차)</t>
+          <t>부산안전산업존(BSI-Zone) 초기창업자 2차 모집공고</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>광주테크노파크</t>
+          <t>부산정보산업진흥원</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Age-Tech 제품 사용성평가 참여자 모집 공고</t>
+          <t>2026년 AX 에이지테크 시장확산 지원사업 모집 공고</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Age-Tech</t>
+          <t>에이지테크, AX</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>중소벤처기업부</t>
+          <t>부산정보산업진흥원</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>『중소기업 AX 우수사례 공모전』참가기업 모집 공고</t>
+          <t>2026 해양문화도시 기반의 에이지테크 실증거점 조성 사업 「CES 2027 통합 부산관」 참가기업 모집 공고</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>AX</t>
+          <t>에이지테크, 실증</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>중소벤처기업부</t>
+          <t>광주테크노파크</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>「지역 중소기업 AI 활용·확산 유공 포상」 후보자 모집 공고</t>
+          <t>「2026년도 연구개발특구진흥재단 광주특구본부」 지역혁신 실증 프로젝트 기획 실증의제 수요조사 공고(2차)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>유공, 포상</t>
+          <t>실증</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>중앙사회서비스원</t>
+          <t>광주테크노파크</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>2026년 사회서비스 종사자 심리상담 지원사업 3기 참여자 모집(~9/30) 2026-09-01 293</t>
+          <t>Age-Tech 제품 사용성평가 참여자 모집 공고</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>사회서비스</t>
+          <t>Age-Tech</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>고령친화산업지원센터</t>
+          <t>한국사회적기업진흥원</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>[공고] 2026년 1차 고령친화우수제품 지정 공고</t>
+          <t>판로지원 플랫폼</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>고령</t>
+          <t>판로</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>고령친화산업지원센터</t>
+          <t>한국사회적기업진흥원</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>[공고] 2026년 고령친화산업 육성 유공자 정부 포상 추천계획 공고</t>
+          <t>협동조합 홍보포털</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>고령, 유공, 포상</t>
+          <t>홍보</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>고령친화산업지원센터</t>
+          <t>한국사회적기업진흥원</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>고령친화우수제품 안내 책자 (2025년 기준)</t>
+          <t>2026년 사회적기업 인증 가이드 서울인천센터</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>고령</t>
+          <t>인증</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>고령친화산업지원센터</t>
+          <t>한국사회적기업진흥원</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2026 홈케어·재활·복지전시회(Reha·Homecare 2026) 연계 고령친화제품 홍보관 운영 계획 및 참가 신청 안내(~6.22(월) 17시까지)</t>
+          <t>2026년 사회적기업 인증 안내 리플릿 서울인천센터</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>고령, 홍보</t>
+          <t>인증</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>[공고] 2026년 1차 고령친화우수제품 지정계획 공고(서류접수 5.11(월) ~ 5.22(금) 17:00까지)</t>
+          <t>[공고] 2026년 1차 고령친화우수제품 지정 공고</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
+          <t>고령친화산업지원센터</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>판로지원 플랫폼</t>
+          <t>[공고] 2026년 고령친화산업 육성 유공자 정부 포상 추천계획 공고</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>판로</t>
+          <t>고령, 유공, 포상</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
+          <t>고령친화산업지원센터</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>협동조합 홍보포털</t>
+          <t>고령친화우수제품 안내 책자 (2025년 기준)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>홍보</t>
+          <t>고령</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
+          <t>고령친화산업지원센터</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>2026년 사회적기업 인증 가이드 서울인천센터</t>
+          <t>2026 홈케어·재활·복지전시회(Reha·Homecare 2026) 연계 고령친화제품 홍보관 운영 계획 및 참가 신청 안내(~6.22(월) 17시까지)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>인증</t>
+          <t>고령, 홍보</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
+          <t>고령친화산업지원센터</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2026년 사회적기업 인증 안내 리플릿 서울인천센터</t>
+          <t>[공고] 2026년 1차 고령친화우수제품 지정계획 공고(서류접수 5.11(월) ~ 5.22(금) 17:00까지)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>인증</t>
+          <t>고령</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1528,8 +1528,74 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>고령친화산업지원센터</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>AI응용제품 신속 상용화(복지분야, 에이지테크 기반 고령친화사업 지원) 컨소시엄 모집 공고(~4.24.(금), 18:00)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>고령, 에이지테크</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>고령친화산업지원센터</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>[공고] 'Age-Tech 종합지원센터 지원사업' 참여기관 모집 공고(~ 3.30(월) 17:00까지)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Age-Tech</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G30"/>
+  <autoFilter ref="A1:G32"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -1560,6 +1626,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
